--- a/1_Data/2. FAO data/A-1_FAO_Cropland_mapping_GLORIA.xlsx
+++ b/1_Data/2. FAO data/A-1_FAO_Cropland_mapping_GLORIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/etber_dtu_dk/Documents/Dokumenter/MRIOS/2022 IATRC Annual meeting/Full_article/1. Data/2. FAO data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mitprod-my.sharepoint.com/personal/etber_mit_edu/Documents/Documents/Deforestation_Nature/Forest_Club_SI/1. Data/2. FAO data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{7166154E-D6B5-4CD0-B78C-D873E30F9568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C390B0A-A592-456E-A2D6-7854FE3D095C}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{7166154E-D6B5-4CD0-B78C-D873E30F9568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66F279DE-5415-4790-B001-2448ADD82760}"/>
   <bookViews>
-    <workbookView xWindow="-67320" yWindow="-3045" windowWidth="38640" windowHeight="21120" xr2:uid="{B0DE4FF8-43CB-4EFF-84BD-D637992F8260}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{B0DE4FF8-43CB-4EFF-84BD-D637992F8260}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="248">
   <si>
     <t>Pomelos and grapefruits</t>
   </si>
@@ -555,15 +555,6 @@
     <t>Cultivation of crops nec</t>
   </si>
   <si>
-    <t>Exiobase Sector</t>
-  </si>
-  <si>
-    <t>GTAP Sector</t>
-  </si>
-  <si>
-    <t>GTAP Code</t>
-  </si>
-  <si>
     <t>Other Grains: maize (corn), sorghum, barley, rye, oats, millets, other cereals</t>
   </si>
   <si>
@@ -787,9 +778,6 @@
   </si>
   <si>
     <t>Raising of poultry</t>
-  </si>
-  <si>
-    <t>GLORIA Sector</t>
   </si>
   <si>
     <t>Raising of animals n.e.c.; services to agriculture</t>
@@ -835,7 +823,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -848,8 +836,14 @@
         <bgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -897,37 +891,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="dashed">
-        <color indexed="64"/>
-      </left>
-      <right style="dashed">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashed">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="dashed">
-        <color indexed="64"/>
-      </right>
-      <top style="dashed">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashed">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
         <color indexed="64"/>
       </left>
       <right style="dashed">
@@ -961,22 +925,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dashed">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dashed">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -985,10 +975,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1097,6 +1097,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6C9D8E55-491B-4F53-AAC7-3D836B36B9F0}" name="Table1" displayName="Table1" ref="A1:F190" headerRowDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="A1:F190" xr:uid="{6C9D8E55-491B-4F53-AAC7-3D836B36B9F0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F187">
+    <sortCondition ref="F1:F190"/>
+  </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{680F209E-1833-48A4-9B20-1687CBFC1607}" name="HILDA+" totalsRowLabel="Total" dataDxfId="4" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3D18FDC3-FA97-47FF-A731-7236B8F8EB92}" name="FAO commodity" dataDxfId="2"/>
@@ -1407,58 +1410,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B19646A-D728-4356-8870-C75B4BA81A1D}">
   <dimension ref="A1:F190"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
-    <col min="3" max="3" width="36.7265625" customWidth="1"/>
-    <col min="4" max="4" width="69.81640625" customWidth="1"/>
-    <col min="5" max="5" width="15.1796875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="36.77734375" customWidth="1"/>
+    <col min="4" max="4" width="69.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" style="7" customWidth="1"/>
     <col min="6" max="6" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="D1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
         <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B3" t="s">
@@ -1468,77 +1471,77 @@
         <v>164</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>189</v>
+        <v>185</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>186</v>
       </c>
       <c r="F3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>170</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
         <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B7" t="s">
@@ -1548,157 +1551,157 @@
         <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F8" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
         <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F9" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="C10" t="s">
         <v>170</v>
       </c>
       <c r="D10" t="s">
-        <v>176</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F10" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>166</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
         <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F12" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
         <v>166</v>
       </c>
       <c r="D13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
         <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B15" t="s">
@@ -1708,137 +1711,137 @@
         <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
         <v>170</v>
       </c>
       <c r="D16" t="s">
-        <v>176</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F16" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F17" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
         <v>166</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F18" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
         <v>166</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F19" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
         <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F20" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
         <v>166</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F21" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B22" t="s">
@@ -1848,57 +1851,57 @@
         <v>168</v>
       </c>
       <c r="D22" t="s">
-        <v>184</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="F22" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
         <v>166</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F23" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
         <v>166</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B25" t="s">
@@ -1908,17 +1911,17 @@
         <v>165</v>
       </c>
       <c r="D25" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F25" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B26" t="s">
@@ -1928,77 +1931,77 @@
         <v>167</v>
       </c>
       <c r="D26" t="s">
-        <v>178</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F26" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
         <v>166</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F27" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
         <v>166</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F28" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
         <v>166</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B30" t="s">
@@ -2008,117 +2011,117 @@
         <v>163</v>
       </c>
       <c r="D30" t="s">
-        <v>180</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="F30" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F31" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
         <v>166</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F32" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
         <v>166</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F33" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
         <v>170</v>
       </c>
       <c r="D34" t="s">
-        <v>176</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F34" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
         <v>166</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F35" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B36" t="s">
@@ -2128,17 +2131,17 @@
         <v>167</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F36" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B37" t="s">
@@ -2148,57 +2151,57 @@
         <v>165</v>
       </c>
       <c r="D37" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
         <v>166</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F38" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
         <v>166</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F39" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B40" t="s">
@@ -2208,17 +2211,17 @@
         <v>165</v>
       </c>
       <c r="D40" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F40" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B41" t="s">
@@ -2228,17 +2231,17 @@
         <v>167</v>
       </c>
       <c r="D41" t="s">
-        <v>178</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F41" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B42" t="s">
@@ -2248,77 +2251,77 @@
         <v>169</v>
       </c>
       <c r="D42" t="s">
-        <v>182</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" t="s">
+        <v>166</v>
+      </c>
+      <c r="D43" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F43" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B43" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" t="s">
-        <v>166</v>
-      </c>
-      <c r="D43" t="s">
-        <v>186</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F43" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="C44" t="s">
         <v>166</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F44" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
         <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F45" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B46" t="s">
@@ -2328,17 +2331,17 @@
         <v>167</v>
       </c>
       <c r="D46" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F46" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B47" t="s">
@@ -2348,117 +2351,117 @@
         <v>167</v>
       </c>
       <c r="D47" t="s">
-        <v>178</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F47" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
         <v>166</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F48" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
         <v>166</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F49" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
         <v>166</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F50" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
         <v>166</v>
       </c>
       <c r="D51" t="s">
-        <v>186</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F51" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
         <v>166</v>
       </c>
       <c r="D52" t="s">
-        <v>186</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F52" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B53" t="s">
@@ -2468,37 +2471,37 @@
         <v>167</v>
       </c>
       <c r="D53" t="s">
-        <v>178</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
         <v>170</v>
       </c>
       <c r="D54" t="s">
-        <v>176</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F54" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B55" t="s">
@@ -2508,57 +2511,57 @@
         <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>178</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F55" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C56" t="s">
         <v>166</v>
       </c>
       <c r="D56" t="s">
-        <v>186</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F56" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s">
         <v>166</v>
       </c>
       <c r="D57" t="s">
-        <v>186</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F57" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B58" t="s">
@@ -2568,57 +2571,57 @@
         <v>169</v>
       </c>
       <c r="D58" t="s">
-        <v>182</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F58" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B59" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" t="s">
+        <v>166</v>
+      </c>
+      <c r="D59" t="s">
+        <v>183</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F59" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B59" t="s">
-        <v>57</v>
-      </c>
-      <c r="C59" t="s">
-        <v>166</v>
-      </c>
-      <c r="D59" t="s">
-        <v>186</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F59" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
         <v>166</v>
       </c>
       <c r="D60" t="s">
-        <v>186</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F60" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B61" t="s">
@@ -2628,17 +2631,17 @@
         <v>167</v>
       </c>
       <c r="D61" t="s">
-        <v>178</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F61" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B62" t="s">
@@ -2648,137 +2651,137 @@
         <v>169</v>
       </c>
       <c r="D62" t="s">
-        <v>182</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F62" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="C63" t="s">
         <v>170</v>
       </c>
       <c r="D63" t="s">
-        <v>176</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F63" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="C64" t="s">
         <v>166</v>
       </c>
       <c r="D64" t="s">
-        <v>186</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F64" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D65" t="s">
-        <v>186</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="C66" t="s">
         <v>170</v>
       </c>
       <c r="D66" t="s">
-        <v>176</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="C67" t="s">
         <v>166</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F67" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="C68" t="s">
         <v>166</v>
       </c>
       <c r="D68" t="s">
-        <v>186</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F68" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B69" t="s">
@@ -2788,57 +2791,57 @@
         <v>167</v>
       </c>
       <c r="D69" t="s">
-        <v>178</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F69" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="C70" t="s">
         <v>166</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F70" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="C71" t="s">
         <v>166</v>
       </c>
       <c r="D71" t="s">
-        <v>186</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F71" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B72" t="s">
@@ -2848,17 +2851,17 @@
         <v>168</v>
       </c>
       <c r="D72" t="s">
-        <v>184</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="F72" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B73" t="s">
@@ -2868,17 +2871,17 @@
         <v>167</v>
       </c>
       <c r="D73" t="s">
-        <v>178</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F73" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B74" t="s">
@@ -2888,17 +2891,17 @@
         <v>165</v>
       </c>
       <c r="D74" t="s">
-        <v>174</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F74" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B75" t="s">
@@ -2908,97 +2911,97 @@
         <v>169</v>
       </c>
       <c r="D75" t="s">
-        <v>182</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F75" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" t="s">
+        <v>166</v>
+      </c>
+      <c r="D76" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F76" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B76" t="s">
-        <v>74</v>
-      </c>
-      <c r="C76" t="s">
-        <v>166</v>
-      </c>
-      <c r="D76" t="s">
-        <v>186</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F76" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C77" t="s">
         <v>166</v>
       </c>
       <c r="D77" t="s">
-        <v>186</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F77" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="C78" t="s">
         <v>166</v>
       </c>
       <c r="D78" t="s">
-        <v>186</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F78" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="C79" t="s">
         <v>166</v>
       </c>
       <c r="D79" t="s">
-        <v>186</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F79" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B80" t="s">
@@ -3008,37 +3011,37 @@
         <v>169</v>
       </c>
       <c r="D80" t="s">
-        <v>182</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F80" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" t="s">
+        <v>145</v>
+      </c>
+      <c r="C81" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" t="s">
+        <v>183</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F81" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B81" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" t="s">
-        <v>166</v>
-      </c>
-      <c r="D81" t="s">
-        <v>186</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F81" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="8" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B82" t="s">
@@ -3048,17 +3051,17 @@
         <v>169</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F82" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B83" t="s">
@@ -3068,57 +3071,57 @@
         <v>169</v>
       </c>
       <c r="D83" t="s">
-        <v>182</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F83" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" t="s">
+        <v>146</v>
+      </c>
+      <c r="C84" t="s">
+        <v>166</v>
+      </c>
+      <c r="D84" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F84" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B84" t="s">
-        <v>82</v>
-      </c>
-      <c r="C84" t="s">
-        <v>166</v>
-      </c>
-      <c r="D84" t="s">
-        <v>186</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F84" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="8" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
         <v>166</v>
       </c>
       <c r="D85" t="s">
-        <v>186</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F85" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B86" t="s">
@@ -3128,17 +3131,17 @@
         <v>165</v>
       </c>
       <c r="D86" t="s">
-        <v>174</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F86" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B87" t="s">
@@ -3148,117 +3151,117 @@
         <v>167</v>
       </c>
       <c r="D87" t="s">
-        <v>178</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F87" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="C88" t="s">
         <v>166</v>
       </c>
       <c r="D88" t="s">
-        <v>186</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F88" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="C89" t="s">
         <v>170</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F89" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="C90" t="s">
         <v>166</v>
       </c>
       <c r="D90" t="s">
-        <v>186</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F90" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C91" t="s">
         <v>166</v>
       </c>
       <c r="D91" t="s">
-        <v>186</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F91" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C92" t="s">
         <v>166</v>
       </c>
       <c r="D92" t="s">
-        <v>186</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F92" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B93" t="s">
@@ -3268,17 +3271,17 @@
         <v>169</v>
       </c>
       <c r="D93" t="s">
-        <v>182</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F93" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B94" t="s">
@@ -3288,97 +3291,97 @@
         <v>165</v>
       </c>
       <c r="D94" t="s">
-        <v>174</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F94" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B95" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" t="s">
+        <v>166</v>
+      </c>
+      <c r="D95" t="s">
+        <v>183</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F95" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B95" t="s">
-        <v>93</v>
-      </c>
-      <c r="C95" t="s">
-        <v>166</v>
-      </c>
-      <c r="D95" t="s">
-        <v>186</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F95" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="8" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B96" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="C96" t="s">
         <v>170</v>
       </c>
       <c r="D96" t="s">
-        <v>176</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F96" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="C97" t="s">
         <v>166</v>
       </c>
       <c r="D97" t="s">
-        <v>186</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F97" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="C98" t="s">
         <v>166</v>
       </c>
       <c r="D98" t="s">
-        <v>186</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B99" t="s">
@@ -3388,117 +3391,117 @@
         <v>167</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F99" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
         <v>166</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F100" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="C101" t="s">
         <v>166</v>
       </c>
       <c r="D101" t="s">
-        <v>186</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="C102" t="s">
         <v>166</v>
       </c>
       <c r="D102" t="s">
-        <v>186</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F102" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="C103" t="s">
         <v>166</v>
       </c>
       <c r="D103" t="s">
-        <v>186</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F103" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="C104" t="s">
         <v>166</v>
       </c>
       <c r="D104" t="s">
-        <v>186</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B105" t="s">
@@ -3508,57 +3511,57 @@
         <v>167</v>
       </c>
       <c r="D105" t="s">
-        <v>178</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F105" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="C106" t="s">
         <v>166</v>
       </c>
       <c r="D106" t="s">
-        <v>186</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F106" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="C107" t="s">
         <v>166</v>
       </c>
       <c r="D107" t="s">
-        <v>186</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F107" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B108" t="s">
@@ -3568,157 +3571,157 @@
         <v>168</v>
       </c>
       <c r="D108" t="s">
-        <v>184</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="F108" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="C109" t="s">
         <v>166</v>
       </c>
       <c r="D109" t="s">
-        <v>186</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F109" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C110" t="s">
         <v>166</v>
       </c>
       <c r="D110" t="s">
-        <v>186</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F110" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="C111" t="s">
         <v>166</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F111" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="C112" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D112" t="s">
-        <v>176</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F112" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="C113" t="s">
         <v>166</v>
       </c>
       <c r="D113" t="s">
-        <v>186</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F113" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="C114" t="s">
         <v>166</v>
       </c>
       <c r="D114" t="s">
-        <v>186</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F114" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="C115" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D115" t="s">
-        <v>176</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F115" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B116" t="s">
@@ -3728,37 +3731,37 @@
         <v>165</v>
       </c>
       <c r="D116" t="s">
-        <v>174</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F116" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B117" t="s">
+        <v>74</v>
+      </c>
+      <c r="C117" t="s">
+        <v>166</v>
+      </c>
+      <c r="D117" t="s">
+        <v>183</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F117" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B117" t="s">
-        <v>115</v>
-      </c>
-      <c r="C117" t="s">
-        <v>166</v>
-      </c>
-      <c r="D117" t="s">
-        <v>186</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F117" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="8" t="s">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B118" t="s">
@@ -3768,17 +3771,17 @@
         <v>169</v>
       </c>
       <c r="D118" t="s">
-        <v>182</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F118" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B119" t="s">
@@ -3788,17 +3791,17 @@
         <v>169</v>
       </c>
       <c r="D119" t="s">
-        <v>182</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F119" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B120" t="s">
@@ -3808,17 +3811,17 @@
         <v>167</v>
       </c>
       <c r="D120" t="s">
-        <v>178</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F120" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B121" t="s">
@@ -3828,97 +3831,97 @@
         <v>165</v>
       </c>
       <c r="D121" t="s">
-        <v>174</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F121" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B122" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="C122" t="s">
         <v>166</v>
       </c>
       <c r="D122" t="s">
-        <v>186</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F122" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C123" t="s">
         <v>166</v>
       </c>
       <c r="D123" t="s">
-        <v>186</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F123" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="C124" t="s">
         <v>166</v>
       </c>
       <c r="D124" t="s">
-        <v>186</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F124" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B125" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="C125" t="s">
         <v>166</v>
       </c>
       <c r="D125" t="s">
-        <v>186</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F125" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B126" t="s">
@@ -3928,117 +3931,117 @@
         <v>167</v>
       </c>
       <c r="D126" t="s">
-        <v>178</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F126" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B127" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C127" t="s">
         <v>166</v>
       </c>
       <c r="D127" t="s">
-        <v>186</v>
-      </c>
-      <c r="E127" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F127" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B128" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C128" t="s">
         <v>166</v>
       </c>
       <c r="D128" t="s">
-        <v>186</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F128" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B129" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C129" t="s">
         <v>166</v>
       </c>
       <c r="D129" t="s">
-        <v>186</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F129" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C130" t="s">
         <v>170</v>
       </c>
       <c r="D130" t="s">
-        <v>176</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F130" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B131" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="C131" t="s">
         <v>166</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
-      </c>
-      <c r="E131" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F131" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A132" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B132" t="s">
@@ -4048,37 +4051,37 @@
         <v>167</v>
       </c>
       <c r="D132" t="s">
-        <v>178</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F132" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A133" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="C133" t="s">
         <v>166</v>
       </c>
       <c r="D133" t="s">
-        <v>186</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F133" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A134" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B134" t="s">
@@ -4088,57 +4091,57 @@
         <v>167</v>
       </c>
       <c r="D134" t="s">
-        <v>178</v>
-      </c>
-      <c r="E134" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F134" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A135" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="C135" t="s">
         <v>166</v>
       </c>
       <c r="D135" t="s">
-        <v>186</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F135" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A136" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B136" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="C136" t="s">
         <v>166</v>
       </c>
       <c r="D136" t="s">
-        <v>186</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F136" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A137" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B137" t="s">
@@ -4148,37 +4151,37 @@
         <v>169</v>
       </c>
       <c r="D137" t="s">
-        <v>182</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="F137" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A138" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="C138" t="s">
         <v>166</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
-      </c>
-      <c r="E138" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F138" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A139" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B139" t="s">
@@ -4188,17 +4191,17 @@
         <v>165</v>
       </c>
       <c r="D139" t="s">
-        <v>174</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F139" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A140" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B140" t="s">
@@ -4208,57 +4211,57 @@
         <v>165</v>
       </c>
       <c r="D140" t="s">
-        <v>174</v>
-      </c>
-      <c r="E140" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F140" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B141" t="s">
+        <v>121</v>
+      </c>
+      <c r="C141" t="s">
+        <v>166</v>
+      </c>
+      <c r="D141" t="s">
+        <v>183</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F141" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A141" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B141" t="s">
-        <v>139</v>
-      </c>
-      <c r="C141" t="s">
-        <v>166</v>
-      </c>
-      <c r="D141" t="s">
-        <v>186</v>
-      </c>
-      <c r="E141" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F141" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A142" s="8" t="s">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C142" t="s">
         <v>166</v>
       </c>
       <c r="D142" t="s">
-        <v>186</v>
-      </c>
-      <c r="E142" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F142" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A143" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B143" t="s">
@@ -4268,117 +4271,117 @@
         <v>170</v>
       </c>
       <c r="D143" t="s">
-        <v>176</v>
-      </c>
-      <c r="E143" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F143" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A144" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B144" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C144" t="s">
         <v>166</v>
       </c>
       <c r="D144" t="s">
-        <v>186</v>
-      </c>
-      <c r="E144" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F144" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A145" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C145" t="s">
         <v>166</v>
       </c>
       <c r="D145" t="s">
-        <v>186</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F145" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A146" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C146" t="s">
         <v>166</v>
       </c>
       <c r="D146" t="s">
-        <v>186</v>
-      </c>
-      <c r="E146" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F146" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A147" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C147" t="s">
         <v>166</v>
       </c>
       <c r="D147" t="s">
-        <v>186</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F147" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A148" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C148" t="s">
         <v>166</v>
       </c>
       <c r="D148" t="s">
-        <v>186</v>
-      </c>
-      <c r="E148" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F148" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A149" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B149" t="s">
@@ -4388,17 +4391,17 @@
         <v>165</v>
       </c>
       <c r="D149" t="s">
-        <v>174</v>
-      </c>
-      <c r="E149" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F149" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A150" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B150" t="s">
@@ -4408,77 +4411,77 @@
         <v>165</v>
       </c>
       <c r="D150" t="s">
-        <v>174</v>
-      </c>
-      <c r="E150" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F150" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B151" t="s">
+        <v>139</v>
+      </c>
+      <c r="C151" t="s">
+        <v>166</v>
+      </c>
+      <c r="D151" t="s">
+        <v>183</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F151" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A151" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B151" t="s">
-        <v>149</v>
-      </c>
-      <c r="C151" t="s">
-        <v>166</v>
-      </c>
-      <c r="D151" t="s">
-        <v>186</v>
-      </c>
-      <c r="E151" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F151" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A152" s="8" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
         <v>170</v>
       </c>
       <c r="D152" t="s">
-        <v>176</v>
-      </c>
-      <c r="E152" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F152" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A153" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B153" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C153" t="s">
         <v>166</v>
       </c>
       <c r="D153" t="s">
-        <v>186</v>
-      </c>
-      <c r="E153" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F153" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A154" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B154" t="s">
@@ -4488,733 +4491,733 @@
         <v>165</v>
       </c>
       <c r="D154" t="s">
-        <v>174</v>
-      </c>
-      <c r="E154" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F154" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" t="s">
+        <v>144</v>
+      </c>
+      <c r="C155" t="s">
+        <v>166</v>
+      </c>
+      <c r="D155" t="s">
+        <v>183</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F155" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A155" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B155" t="s">
-        <v>153</v>
-      </c>
-      <c r="C155" t="s">
-        <v>166</v>
-      </c>
-      <c r="D155" t="s">
-        <v>186</v>
-      </c>
-      <c r="E155" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F155" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A156" s="8" t="s">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B156" t="s">
+        <v>149</v>
+      </c>
+      <c r="C156" t="s">
+        <v>166</v>
+      </c>
+      <c r="D156" t="s">
+        <v>183</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F156" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B157" t="s">
         <v>154</v>
       </c>
-      <c r="C156" t="s">
-        <v>166</v>
-      </c>
-      <c r="D156" t="s">
-        <v>186</v>
-      </c>
-      <c r="E156" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F156" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A157" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
+        <v>166</v>
+      </c>
+      <c r="D157" t="s">
+        <v>183</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F157" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B158" t="s">
         <v>155</v>
       </c>
-      <c r="C157" t="s">
-        <v>166</v>
-      </c>
-      <c r="D157" t="s">
-        <v>186</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F157" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A158" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
+        <v>166</v>
+      </c>
+      <c r="D158" t="s">
+        <v>183</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F158" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159" t="s">
         <v>156</v>
       </c>
-      <c r="C158" t="s">
-        <v>166</v>
-      </c>
-      <c r="D158" t="s">
-        <v>186</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F158" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A159" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B159" t="s">
-        <v>157</v>
-      </c>
       <c r="C159" t="s">
         <v>166</v>
       </c>
       <c r="D159" t="s">
-        <v>186</v>
-      </c>
-      <c r="E159" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F159" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A160" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="C160" t="s">
         <v>170</v>
       </c>
       <c r="D160" t="s">
-        <v>176</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="F160" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B161" t="s">
+        <v>193</v>
+      </c>
+      <c r="C161" t="s">
+        <v>213</v>
+      </c>
+      <c r="D161" t="s">
+        <v>187</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F161" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B162" t="s">
+        <v>194</v>
+      </c>
+      <c r="C162" t="s">
+        <v>211</v>
+      </c>
+      <c r="D162" t="s">
+        <v>209</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F162" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B163" t="s">
+        <v>195</v>
+      </c>
+      <c r="C163" t="s">
+        <v>192</v>
+      </c>
+      <c r="D163" t="s">
+        <v>187</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B164" t="s">
+        <v>196</v>
+      </c>
+      <c r="C164" t="s">
+        <v>213</v>
+      </c>
+      <c r="D164" t="s">
+        <v>187</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F164" s="11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B165" t="s">
+        <v>197</v>
+      </c>
+      <c r="C165" t="s">
+        <v>192</v>
+      </c>
+      <c r="D165" t="s">
+        <v>187</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F165" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B166" t="s">
+        <v>198</v>
+      </c>
+      <c r="C166" t="s">
+        <v>192</v>
+      </c>
+      <c r="D166" t="s">
+        <v>187</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F166" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B167" t="s">
+        <v>199</v>
+      </c>
+      <c r="C167" t="s">
+        <v>211</v>
+      </c>
+      <c r="D167" t="s">
+        <v>209</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F167" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B168" t="s">
+        <v>200</v>
+      </c>
+      <c r="C168" t="s">
+        <v>212</v>
+      </c>
+      <c r="D168" t="s">
+        <v>209</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F168" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A161" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B161" t="s">
-        <v>196</v>
-      </c>
-      <c r="C161" t="s">
-        <v>216</v>
-      </c>
-      <c r="D161" t="s">
-        <v>190</v>
-      </c>
-      <c r="E161" s="10" t="s">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="F161" t="s">
+      <c r="B169" t="s">
+        <v>201</v>
+      </c>
+      <c r="C169" t="s">
+        <v>211</v>
+      </c>
+      <c r="D169" t="s">
+        <v>209</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F169" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A162" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B162" t="s">
-        <v>197</v>
-      </c>
-      <c r="C162" t="s">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B170" t="s">
+        <v>202</v>
+      </c>
+      <c r="C170" t="s">
+        <v>211</v>
+      </c>
+      <c r="D170" t="s">
+        <v>209</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F170" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B171" t="s">
+        <v>203</v>
+      </c>
+      <c r="C171" t="s">
+        <v>213</v>
+      </c>
+      <c r="D171" t="s">
+        <v>209</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F171" s="11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B172" t="s">
+        <v>204</v>
+      </c>
+      <c r="C172" t="s">
+        <v>213</v>
+      </c>
+      <c r="D172" t="s">
+        <v>187</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F172" s="11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B173" t="s">
+        <v>205</v>
+      </c>
+      <c r="C173" t="s">
+        <v>211</v>
+      </c>
+      <c r="D173" t="s">
+        <v>209</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F173" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B174" t="s">
+        <v>206</v>
+      </c>
+      <c r="C174" t="s">
+        <v>192</v>
+      </c>
+      <c r="D174" t="s">
+        <v>187</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F174" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B175" t="s">
+        <v>207</v>
+      </c>
+      <c r="C175" t="s">
+        <v>192</v>
+      </c>
+      <c r="D175" t="s">
+        <v>187</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F175" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B176" t="s">
+        <v>208</v>
+      </c>
+      <c r="C176" t="s">
+        <v>192</v>
+      </c>
+      <c r="D176" t="s">
+        <v>187</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F176" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B177" t="s">
         <v>214</v>
-      </c>
-      <c r="D162" t="s">
-        <v>212</v>
-      </c>
-      <c r="E162" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F162" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A163" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B163" t="s">
-        <v>198</v>
-      </c>
-      <c r="C163" t="s">
-        <v>195</v>
-      </c>
-      <c r="D163" t="s">
-        <v>190</v>
-      </c>
-      <c r="E163" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F163" s="14" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A164" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B164" t="s">
-        <v>199</v>
-      </c>
-      <c r="C164" t="s">
-        <v>216</v>
-      </c>
-      <c r="D164" t="s">
-        <v>190</v>
-      </c>
-      <c r="E164" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F164" s="14" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A165" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B165" t="s">
-        <v>200</v>
-      </c>
-      <c r="C165" t="s">
-        <v>195</v>
-      </c>
-      <c r="D165" t="s">
-        <v>190</v>
-      </c>
-      <c r="E165" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F165" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A166" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B166" t="s">
-        <v>201</v>
-      </c>
-      <c r="C166" t="s">
-        <v>195</v>
-      </c>
-      <c r="D166" t="s">
-        <v>190</v>
-      </c>
-      <c r="E166" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F166" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A167" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B167" t="s">
-        <v>202</v>
-      </c>
-      <c r="C167" t="s">
-        <v>214</v>
-      </c>
-      <c r="D167" t="s">
-        <v>212</v>
-      </c>
-      <c r="E167" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F167" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A168" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B168" t="s">
-        <v>203</v>
-      </c>
-      <c r="C168" t="s">
-        <v>215</v>
-      </c>
-      <c r="D168" t="s">
-        <v>212</v>
-      </c>
-      <c r="E168" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F168" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A169" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B169" t="s">
-        <v>204</v>
-      </c>
-      <c r="C169" t="s">
-        <v>214</v>
-      </c>
-      <c r="D169" t="s">
-        <v>212</v>
-      </c>
-      <c r="E169" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F169" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A170" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B170" t="s">
-        <v>205</v>
-      </c>
-      <c r="C170" t="s">
-        <v>214</v>
-      </c>
-      <c r="D170" t="s">
-        <v>212</v>
-      </c>
-      <c r="E170" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F170" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A171" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B171" t="s">
-        <v>206</v>
-      </c>
-      <c r="C171" t="s">
-        <v>216</v>
-      </c>
-      <c r="D171" t="s">
-        <v>212</v>
-      </c>
-      <c r="E171" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F171" s="14" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A172" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B172" t="s">
-        <v>207</v>
-      </c>
-      <c r="C172" t="s">
-        <v>216</v>
-      </c>
-      <c r="D172" t="s">
-        <v>190</v>
-      </c>
-      <c r="E172" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F172" s="14" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A173" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B173" t="s">
-        <v>208</v>
-      </c>
-      <c r="C173" t="s">
-        <v>214</v>
-      </c>
-      <c r="D173" t="s">
-        <v>212</v>
-      </c>
-      <c r="E173" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F173" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A174" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B174" t="s">
-        <v>209</v>
-      </c>
-      <c r="C174" t="s">
-        <v>195</v>
-      </c>
-      <c r="D174" t="s">
-        <v>190</v>
-      </c>
-      <c r="E174" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F174" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A175" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B175" t="s">
-        <v>210</v>
-      </c>
-      <c r="C175" t="s">
-        <v>195</v>
-      </c>
-      <c r="D175" t="s">
-        <v>190</v>
-      </c>
-      <c r="E175" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F175" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A176" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B176" t="s">
-        <v>211</v>
-      </c>
-      <c r="C176" t="s">
-        <v>195</v>
-      </c>
-      <c r="D176" t="s">
-        <v>190</v>
-      </c>
-      <c r="E176" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F176" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A177" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B177" t="s">
-        <v>217</v>
       </c>
       <c r="C177" t="s">
         <v>167</v>
       </c>
       <c r="D177" t="s">
-        <v>178</v>
-      </c>
-      <c r="E177" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F177" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A178" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B178" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C178" t="s">
         <v>165</v>
       </c>
       <c r="D178" t="s">
-        <v>174</v>
-      </c>
-      <c r="E178" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F178" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A179" s="11" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B179" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C179" t="s">
         <v>167</v>
       </c>
       <c r="D179" t="s">
-        <v>178</v>
-      </c>
-      <c r="E179" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F179" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A180" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B180" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C180" t="s">
         <v>164</v>
       </c>
       <c r="D180" t="s">
-        <v>188</v>
-      </c>
-      <c r="E180" s="10" t="s">
-        <v>189</v>
+        <v>185</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>186</v>
       </c>
       <c r="F180" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A181" s="11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B181" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C181" t="s">
         <v>168</v>
       </c>
       <c r="D181" t="s">
-        <v>184</v>
-      </c>
-      <c r="E181" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="F181" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A182" s="11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B182" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C182" t="s">
         <v>167</v>
       </c>
       <c r="D182" t="s">
-        <v>178</v>
-      </c>
-      <c r="E182" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F182" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A183" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B183" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C183" t="s">
         <v>168</v>
       </c>
       <c r="D183" t="s">
-        <v>184</v>
-      </c>
-      <c r="E183" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="F183" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A184" s="11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B184" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C184" t="s">
         <v>163</v>
       </c>
       <c r="D184" t="s">
-        <v>180</v>
-      </c>
-      <c r="E184" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="F184" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A185" s="11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B185" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C185" t="s">
         <v>166</v>
       </c>
       <c r="D185" t="s">
-        <v>186</v>
-      </c>
-      <c r="E185" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F185" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A186" s="11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B186" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C186" t="s">
         <v>165</v>
       </c>
       <c r="D186" t="s">
-        <v>174</v>
-      </c>
-      <c r="E186" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="F186" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B187" t="s">
+        <v>224</v>
+      </c>
+      <c r="C187" t="s">
+        <v>166</v>
+      </c>
+      <c r="D187" t="s">
+        <v>183</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F187" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A187" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B187" t="s">
-        <v>227</v>
-      </c>
-      <c r="C187" t="s">
-        <v>166</v>
-      </c>
-      <c r="D187" t="s">
-        <v>186</v>
-      </c>
-      <c r="E187" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F187" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A188" s="11" t="s">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B188" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C188" t="s">
         <v>167</v>
       </c>
       <c r="D188" t="s">
-        <v>178</v>
-      </c>
-      <c r="E188" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F188" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A189" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B189" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C189" t="s">
         <v>167</v>
       </c>
       <c r="D189" t="s">
-        <v>178</v>
-      </c>
-      <c r="E189" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="F189" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A190" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B190" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C190" t="s">
         <v>164</v>
       </c>
       <c r="D190" t="s">
-        <v>188</v>
-      </c>
-      <c r="E190" s="10" t="s">
-        <v>189</v>
+        <v>185</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>186</v>
       </c>
       <c r="F190" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -5227,194 +5230,155 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF840DB8-77E3-426D-9B03-0BB794815A34}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.08984375" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" customWidth="1"/>
-    <col min="4" max="4" width="31.90625" customWidth="1"/>
-    <col min="9" max="9" width="27.7265625" customWidth="1"/>
+    <col min="1" max="1" width="69.77734375" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="7" max="7" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B11" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="B12" s="12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B15" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="B16" s="12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
+      <c r="B18" s="12" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>